--- a/AtchisonRegime/Outputs/China/ASX300_Materials/df_regSummary_ASX300_Materials.xlsx
+++ b/AtchisonRegime/Outputs/China/ASX300_Materials/df_regSummary_ASX300_Materials.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6880661859561092</v>
+        <v>0.6552474316875557</v>
       </c>
       <c r="H2" t="n">
-        <v>3.879511980592399</v>
+        <v>3.801372264025864</v>
       </c>
       <c r="I2" t="n">
         <v>-4.51216419039352</v>
@@ -545,19 +545,19 @@
         <v>8.772867259703339</v>
       </c>
       <c r="K2" t="n">
-        <v>24</v>
+        <v>24.75247524752475</v>
       </c>
       <c r="L2" t="n">
         <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03295657691296942</v>
+        <v>0.03270904923642388</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.06524666334535389</v>
+        <v>-0.06648430172808162</v>
       </c>
       <c r="P2" t="n">
         <v>0.1563695383719861</v>
@@ -603,7 +603,7 @@
         <v>16.133821600917</v>
       </c>
       <c r="K3" t="n">
-        <v>23</v>
+        <v>22.77227722772277</v>
       </c>
       <c r="L3" t="n">
         <v>4</v>
@@ -661,7 +661,7 @@
         <v>12.9481215237874</v>
       </c>
       <c r="K4" t="n">
-        <v>30</v>
+        <v>29.7029702970297</v>
       </c>
       <c r="L4" t="n">
         <v>3</v>
@@ -719,7 +719,7 @@
         <v>7.437988740612401</v>
       </c>
       <c r="K5" t="n">
-        <v>23</v>
+        <v>22.77227722772277</v>
       </c>
       <c r="L5" t="n">
         <v>3</v>
